--- a/reviewer_stats_10.xlsx
+++ b/reviewer_stats_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,160 @@
         <v>14565</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>212</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BOBA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>62</v>
+      </c>
+      <c r="D34" t="n">
+        <v>53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48700</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31967</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>218</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BOWWOW</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>46</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24700</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>220</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BROS.</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21876</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22755</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>227</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Balrog</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>304</v>
+      </c>
+      <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
+        <v>190795</v>
+      </c>
+      <c r="F37" t="n">
+        <v>103753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>232</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bebe</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>27</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21114</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9806</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>237</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Beretta</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>97</v>
+      </c>
+      <c r="E39" t="n">
+        <v>71802</v>
+      </c>
+      <c r="F39" t="n">
+        <v>61487</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>250</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bridget</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" t="n">
+        <v>67</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39378</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reviewer_stats_10.xlsx
+++ b/reviewer_stats_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,842 @@
         <v>139393</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>*まみこ*</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3" t="n">
+        <v>52070</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40104</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>03XJR400R</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15418</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10357</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10329</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32102</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60837</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4U</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17794</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12835</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>53羽の孔雀</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17938</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>54dayo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>27</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12635</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10796</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17787</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9464</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41194</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25443</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8bit</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11641</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A.O.D</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>294</v>
+      </c>
+      <c r="D13" t="n">
+        <v>320</v>
+      </c>
+      <c r="E13" t="n">
+        <v>151714</v>
+      </c>
+      <c r="F13" t="n">
+        <v>73661</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AIRS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35457</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29480</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>59200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>51551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AKi</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17108</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5325</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ALEC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34123</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>151</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AXL侍</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29219</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25707</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>153</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A_sui</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21312</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13661</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>154</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acoustic</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12612</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>155</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>22466</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16346</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>162</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11180</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>164</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Andrej</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>130</v>
+      </c>
+      <c r="D23" t="n">
+        <v>169</v>
+      </c>
+      <c r="E23" t="n">
+        <v>90152</v>
+      </c>
+      <c r="F23" t="n">
+        <v>95073</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>165</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Andy17</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>69</v>
+      </c>
+      <c r="D24" t="n">
+        <v>116</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55365</v>
+      </c>
+      <c r="F24" t="n">
+        <v>72004</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>169</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13846</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8313</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>174</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Arufu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>270</v>
+      </c>
+      <c r="D26" t="n">
+        <v>210</v>
+      </c>
+      <c r="E26" t="n">
+        <v>163582</v>
+      </c>
+      <c r="F26" t="n">
+        <v>71393</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>175</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asann</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>58</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>49455</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33123</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>179</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aキト</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>51</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="n">
+        <v>52966</v>
+      </c>
+      <c r="F28" t="n">
+        <v>20191</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>181</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aｓ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14213</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>185</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B.G Lisa</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11591</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>187</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B.Rabbit</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20037</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10146</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>189</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BAMBI</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>90</v>
+      </c>
+      <c r="D32" t="n">
+        <v>59</v>
+      </c>
+      <c r="E32" t="n">
+        <v>73225</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26551</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>190</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BAN/</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>31312</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14565</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>212</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BOBA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>62</v>
+      </c>
+      <c r="D34" t="n">
+        <v>53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48700</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31967</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>218</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BOWWOW</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>46</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24700</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>220</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BROS.</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21876</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22755</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>227</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Balrog</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>304</v>
+      </c>
+      <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
+        <v>190795</v>
+      </c>
+      <c r="F37" t="n">
+        <v>103753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>232</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bebe</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>27</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21114</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9806</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>237</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Beretta</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>97</v>
+      </c>
+      <c r="E39" t="n">
+        <v>71802</v>
+      </c>
+      <c r="F39" t="n">
+        <v>61487</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>250</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bridget</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" t="n">
+        <v>67</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39378</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22365</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reviewer_stats_10.xlsx
+++ b/reviewer_stats_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,468 @@
         <v>139393</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>*まみこ*</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3" t="n">
+        <v>63</v>
+      </c>
+      <c r="E3" t="n">
+        <v>52070</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40104</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>03XJR400R</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15418</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10357</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10329</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32102</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60837</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4U</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17794</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12835</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>53羽の孔雀</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17938</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>54dayo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>27</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12635</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10796</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17787</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9464</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>41194</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25443</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8bit</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11641</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A.O.D</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>294</v>
+      </c>
+      <c r="D13" t="n">
+        <v>320</v>
+      </c>
+      <c r="E13" t="n">
+        <v>151714</v>
+      </c>
+      <c r="F13" t="n">
+        <v>73661</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AIRS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>51</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35457</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29480</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>59200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>51551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AKi</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17108</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5325</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ALEC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34123</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>151</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AXL侍</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E18" t="n">
+        <v>29219</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25707</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>153</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A_sui</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21312</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13661</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>154</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acoustic</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12612</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>155</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ad</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>22466</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16346</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>162</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11180</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>164</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Andrej</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>130</v>
+      </c>
+      <c r="D23" t="n">
+        <v>169</v>
+      </c>
+      <c r="E23" t="n">
+        <v>90152</v>
+      </c>
+      <c r="F23" t="n">
+        <v>95073</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reviewer_stats_10.xlsx
+++ b/reviewer_stats_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>reviewer_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>reviewer_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>liked_movie_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>disliked_movie_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>liked_review_count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>disliked_review_count</t>
         </is>
@@ -942,6 +930,380 @@
       </c>
       <c r="F23" t="n">
         <v>95073</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>165</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Andy17</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>69</v>
+      </c>
+      <c r="D24" t="n">
+        <v>116</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55365</v>
+      </c>
+      <c r="F24" t="n">
+        <v>72004</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>169</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13846</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8313</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>174</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Arufu</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>270</v>
+      </c>
+      <c r="D26" t="n">
+        <v>210</v>
+      </c>
+      <c r="E26" t="n">
+        <v>163582</v>
+      </c>
+      <c r="F26" t="n">
+        <v>71393</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>175</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Asann</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>58</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>49455</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33123</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>179</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aキト</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>51</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="n">
+        <v>52966</v>
+      </c>
+      <c r="F28" t="n">
+        <v>20191</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>181</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aｓ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26</v>
+      </c>
+      <c r="E29" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14213</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>185</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>B.G Lisa</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11591</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>187</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B.Rabbit</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>20037</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10146</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>189</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BAMBI</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>90</v>
+      </c>
+      <c r="D32" t="n">
+        <v>59</v>
+      </c>
+      <c r="E32" t="n">
+        <v>73225</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26551</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>190</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BAN/</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>31312</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14565</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>212</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BOBA</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>62</v>
+      </c>
+      <c r="D34" t="n">
+        <v>53</v>
+      </c>
+      <c r="E34" t="n">
+        <v>48700</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31967</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>218</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BOWWOW</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>46</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24700</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>220</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BROS.</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>51</v>
+      </c>
+      <c r="E36" t="n">
+        <v>21876</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22755</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>227</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Balrog</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>304</v>
+      </c>
+      <c r="D37" t="n">
+        <v>212</v>
+      </c>
+      <c r="E37" t="n">
+        <v>190795</v>
+      </c>
+      <c r="F37" t="n">
+        <v>103753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>232</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bebe</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>27</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21114</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9806</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>237</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Beretta</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>97</v>
+      </c>
+      <c r="E39" t="n">
+        <v>71802</v>
+      </c>
+      <c r="F39" t="n">
+        <v>61487</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>250</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bridget</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" t="n">
+        <v>67</v>
+      </c>
+      <c r="E40" t="n">
+        <v>39378</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22365</v>
       </c>
     </row>
   </sheetData>
